--- a/backtest_runs/20260410_193731/by_symbol/KOIL/KOIL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/KOIL/KOIL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-9154.98</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>104788.24</v>
@@ -817,7 +817,7 @@
         <v>-2090.640000000004</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>114819.94</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>114819.94</v>
@@ -909,7 +909,7 @@
         <v>-286.6200000000028</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>114533.32</v>
@@ -1001,7 +1001,7 @@
         <v>-944.1599999999919</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>114145.54</v>
@@ -1047,7 +1047,7 @@
         <v>-859.8600000000087</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>113285.68</v>
@@ -1277,7 +1277,7 @@
         <v>-11700.84000000001</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>116994.88</v>
@@ -1415,7 +1415,7 @@
         <v>-5041.139999999991</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>120366.88</v>
@@ -1553,7 +1553,7 @@
         <v>-2090.639999999991</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>131072.98</v>
